--- a/dataset/02.wo_Defects/littlemem_st.xlsx
+++ b/dataset/02.wo_Defects/littlemem_st.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>#define MAX_STR 10 #define MAX_3 1 typedef struct { int a; int b; int c; } littlemem_st_006_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[12]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[12]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[12]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[12]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[12]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[12]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[12]; extern volatile int vflag; void littlemem_st_006 () { littlemem_st_006_func_001(); littlemem_st_006_func_002(10); } void littlemem_st_006_func_001 () { littlemem_st_006_s_001_gbl_str = (littlemem_st_006_s_001 *)littlemem_st_006_gbl_buf; } void littlemem_st_006_func_002 (int flag) { if(flag == MAX_STR) { littlemem_st_006_s_001_gbl_str-&gt;c = 1; /*Tool should not detect this line as error*/ /*No ERROR:Little Memory or Overflow*/ } } else if(flag == MAX_3) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should not detect this line as error*/ /*No ERROR:Little Memory or Overflow*/ }</t>
+          <t>#define MAX_STR 10 #define MAX_3 1 typedef struct { int a; int b; int c; } littlemem_st_006_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[12]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[12]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[12]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[12]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[12]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[12]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[12]; extern volatile int vflag; void littlemem_st_006 () { littlemem_st_006_func_001(); littlemem_st_006_func_002(10); } void littlemem_st_006_func_002 (int flag) { if(flag == MAX_STR) { littlemem_st_006_s_001_gbl_str-&gt;c = 1; /*Tool should not detect this line as error*/ /*No ERROR:Little Memory or Overflow*/ } } else if(flag == MAX_3) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should not detect this line as error*/ /*No ERROR:Little Memory or Overflow*/ } void littlemem_st_006_func_001 () { littlemem_st_006_s_001_gbl_str = (littlemem_st_006_s_001 *)littlemem_st_006_gbl_buf; }</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>#define MAX_STR 10 #define MAX_STR1 10 #define MAX_3 1 typedef struct { int a; int b; int c; } littlemem_st_007_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[12]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[12]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[12]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[12]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[12]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[12]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[12]; extern volatile int vflag; void littlemem_st_007 () { littlemem_st_007_func_001(); littlemem_st_007_func_002(1); } void littlemem_st_007_func_002 (int flag) { int i; for(i=0;i&lt;2;i++) { if(flag == MAX_STR1) { ; } else { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should not detect this line as error*/ /*No ERROR:Little Memory or Overflow*/ } } } else if(flag == MAX_3) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should not detect this line as error*/ /*No ERROR:Little Memory or Overflow*/ } void littlemem_st_007_func_001 () { littlemem_st_007_s_001_gbl_str = (littlemem_st_007_s_001 *)littlemem_st_007_gbl_buf; }</t>
+          <t>#define MAX_STR 10 #define MAX_STR1 10 #define MAX_3 1 typedef struct { int a; int b; int c; } littlemem_st_007_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[12]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[12]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[12]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[12]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[12]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[12]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[12]; extern volatile int vflag; void littlemem_st_007 () { littlemem_st_007_func_001(); littlemem_st_007_func_002(1); } void littlemem_st_007_func_001 () { littlemem_st_007_s_001_gbl_str = (littlemem_st_007_s_001 *)littlemem_st_007_gbl_buf; } void littlemem_st_007_func_002 (int flag) { int i; for(i=0;i&lt;2;i++) { if(flag == MAX_STR1) { ; } else { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should not detect this line as error*/ /*No ERROR:Little Memory or Overflow*/ } } } else if(flag == MAX_3) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should not detect this line as error*/ /*No ERROR:Little Memory or Overflow*/ }</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>#define MAX_STR 10 #define MAX_STR2 10 #define MAX_STR3 1 #define MAX_3 1 typedef struct { int a; int b; int c; } littlemem_st_008_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[12]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[12]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[12]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[12]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[12]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[12]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[12]; extern volatile int vflag; void littlemem_st_008 () { littlemem_st_008_func_001(); littlemem_st_008_func_002(1); } void littlemem_st_008_func_002 (int flag) { int i=0; while(i&lt;2) { if(flag == MAX_STR2) { ; } else if(flag == MAX_STR3) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should not detect this line as error*/ /*No ERROR:Little Memory or Overflow*/ } i++; } } else if(flag == MAX_3) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should not detect this line as error*/ /*No ERROR:Little Memory or Overflow*/ } void littlemem_st_008_func_001 () { littlemem_st_008_s_001_gbl_str = (littlemem_st_008_s_001 *)littlemem_st_008_gbl_buf; }</t>
+          <t>#define MAX_STR 10 #define MAX_STR2 10 #define MAX_STR3 1 #define MAX_3 1 typedef struct { int a; int b; int c; } littlemem_st_008_s_001; littlemem_st_004_s_001 *littlemem_st_004_s_001_gbl_str; littlemem_st_005_s_001 *littlemem_st_005_s_001_gbl_str; char littlemem_st_005_gbl_buf[12]; littlemem_st_006_s_001 *littlemem_st_006_s_001_gbl_str; char littlemem_st_006_gbl_buf[12]; littlemem_st_007_s_001 *littlemem_st_007_s_001_gbl_str; char littlemem_st_007_gbl_buf[12]; littlemem_st_008_s_001 *littlemem_st_008_s_001_gbl_str; char littlemem_st_008_gbl_buf[12]; littlemem_st_009_s_001 *littlemem_st_009_s_001_gbl_str; char littlemem_st_009_gbl_buf[12]; littlemem_st_010_s_001 *littlemem_st_010_s_001_gbl_str; char littlemem_st_010_gbl_buf[12]; littlemem_st_011_s_001 *littlemem_st_011_s_001_gbl_str; char littlemem_st_011_gbl_buf[12]; extern volatile int vflag; void littlemem_st_008 () { littlemem_st_008_func_001(); littlemem_st_008_func_002(1); } void littlemem_st_008_func_001 () { littlemem_st_008_s_001_gbl_str = (littlemem_st_008_s_001 *)littlemem_st_008_gbl_buf; } void littlemem_st_008_func_002 (int flag) { int i=0; while(i&lt;2) { if(flag == MAX_STR2) { ; } else if(flag == MAX_STR3) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should not detect this line as error*/ /*No ERROR:Little Memory or Overflow*/ } i++; } } else if(flag == MAX_3) { littlemem_st_007_s_001_gbl_str-&gt;c = 1; /*Tool should not detect this line as error*/ /*No ERROR:Little Memory or Overflow*/ }</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
